--- a/config/tutorial/tutorial_DL.xlsx
+++ b/config/tutorial/tutorial_DL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/tutorial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F8622A-8E0E-411A-9373-B5C51A9DF58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{12F8622A-8E0E-411A-9373-B5C51A9DF58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84320E69-F2B9-4B47-96A2-D944BF64E4DB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-72" yWindow="2592" windowWidth="18216" windowHeight="12120" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="265">
   <si>
     <t>#</t>
   </si>
@@ -883,6 +883,27 @@
   </si>
   <si>
     <t>The strides describe the overlab from one window to the next window.</t>
+  </si>
+  <si>
+    <t>Loss function</t>
+  </si>
+  <si>
+    <t>Loss function for the optimizer:
+1) mse
+2) mae
+3) huber
+4) custom</t>
+  </si>
+  <si>
+    <t>Seq2Seq or Seq2Point</t>
+  </si>
+  <si>
+    <t>Selects if the output nodes should be a squence or single sample:
+0) Sequence equal to window length W
+x) Positiv integer focus point of the window W (must be smaller or equal to W)</t>
+  </si>
+  <si>
+    <t>seq</t>
   </si>
 </sst>
 </file>
@@ -1470,6 +1491,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2735,7 +2760,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -3410,23 +3435,23 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="B30" s="26" t="s">
+    <row r="30" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>213</v>
+      <c r="C30" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>23</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F30" s="9">
+        <v>48</v>
+      </c>
+      <c r="F30" s="10">
         <v>1</v>
       </c>
       <c r="G30" s="31" t="s">
@@ -3435,91 +3460,91 @@
     </row>
     <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>206</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>49</v>
       </c>
       <c r="F31" s="9">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>206</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="6">
-        <v>10</v>
+        <v>49</v>
+      </c>
+      <c r="F32" s="9">
+        <v>1E-3</v>
       </c>
       <c r="G32" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>206</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="G33" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F33" s="6">
+        <v>10</v>
+      </c>
+      <c r="G33" s="31" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>206</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="6">
-        <v>100</v>
+        <v>49</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0.5</v>
       </c>
       <c r="G34" s="29" t="s">
         <v>16</v>
@@ -3527,366 +3552,394 @@
     </row>
     <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>206</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>48</v>
       </c>
       <c r="F35" s="6">
-        <v>1024</v>
+        <v>100</v>
       </c>
       <c r="G35" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>206</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>48</v>
       </c>
       <c r="F36" s="6">
-        <v>3</v>
+        <v>1024</v>
       </c>
       <c r="G36" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="B37" s="39" t="s">
+    <row r="37" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="C37" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="D37" s="39" t="s">
-        <v>231</v>
+      <c r="C37" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>225</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>48</v>
       </c>
       <c r="F37" s="6">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="G37" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B38" s="39" t="s">
         <v>206</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E38" s="26" t="s">
         <v>48</v>
       </c>
       <c r="F38" s="6">
+        <v>600</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="D39" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="6">
         <v>5</v>
       </c>
-      <c r="G38" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="14" t="s">
+      <c r="G39" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A40" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="F40" s="6">
+        <v>600</v>
+      </c>
+      <c r="G40" s="41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B41" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D41" s="27" t="s">
         <v>227</v>
       </c>
-      <c r="E39" s="27" t="s">
+      <c r="E41" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F41" s="10">
         <v>5</v>
       </c>
-      <c r="G39" s="30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="12" t="s">
+      <c r="G41" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B42" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C42" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D42" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="E42" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="48">
+      <c r="F42" s="48">
         <v>1</v>
       </c>
-      <c r="G40" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="13" t="s">
+      <c r="G42" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B43" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D43" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="E43" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F43" s="6">
         <v>1</v>
       </c>
-      <c r="G41" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="14" t="s">
+      <c r="G43" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B44" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C44" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D44" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="E42" s="27" t="s">
+      <c r="E44" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F44" s="10">
         <v>100</v>
       </c>
-      <c r="G42" s="30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="12" t="s">
+      <c r="G44" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B45" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C45" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D43" s="28" t="s">
+      <c r="D45" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="E43" s="28" t="s">
+      <c r="E45" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F45" s="9">
         <v>1</v>
       </c>
-      <c r="G43" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
+      <c r="G45" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B46" s="26" t="s">
         <v>242</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D44" s="26" t="s">
+      <c r="D46" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="E44" s="26" t="s">
+      <c r="E46" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F46" s="6">
         <v>100</v>
       </c>
-      <c r="G44" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="14" t="s">
+      <c r="G46" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B47" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C47" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D47" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="E45" s="27" t="s">
+      <c r="E47" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F47" s="10">
         <v>50</v>
       </c>
-      <c r="G45" s="30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="12" t="s">
+      <c r="G47" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B48" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D46" s="28" t="s">
+      <c r="D48" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="E46" s="28" t="s">
+      <c r="E48" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F48" s="9">
         <v>100</v>
       </c>
-      <c r="G46" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="13" t="s">
+      <c r="G48" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="s">
         <v>250</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="E47" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F47" s="6">
-        <v>3</v>
-      </c>
-      <c r="G47" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="E48" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F48" s="6">
-        <v>32</v>
-      </c>
-      <c r="G48" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A49" s="13" t="s">
-        <v>256</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>248</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="6">
+        <v>3</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" s="6">
+        <v>32</v>
+      </c>
+      <c r="G50" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A51" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" s="9">
         <v>1</v>
       </c>
-      <c r="G49" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="29"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="29"/>
+      <c r="G51" s="29" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
@@ -3906,18 +3959,36 @@
       <c r="F53" s="6"/>
       <c r="G53" s="29"/>
     </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="13"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="29"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="13"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="29"/>
+    </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F50:F53" xr:uid="{8B2ACB76-ED7E-4BDF-9A85-B2112F39B866}">
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F52:F55" xr:uid="{8B2ACB76-ED7E-4BDF-9A85-B2112F39B866}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F38" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F39" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21 F41 F43" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21 F43 F45" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36 F40 F49 F47" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F37 F42 F51 F49" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3938,13 +4009,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{6B215F84-9F1B-41AC-8192-16AB63AE3266}">
       <formula1>"0, 1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22 F30" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39 F44:F46 F42 F48" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F50 F33 F35:F36 F38 F41 F46:F48 F44 F29" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F31:F32 F34" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40" xr:uid="{B64C6103-4646-4D2C-93B2-DA293D23B25B}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/tutorial/tutorial_DL.xlsx
+++ b/config/tutorial/tutorial_DL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/tutorial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{12F8622A-8E0E-411A-9373-B5C51A9DF58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84320E69-F2B9-4B47-96A2-D944BF64E4DB}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{12F8622A-8E0E-411A-9373-B5C51A9DF58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B987C89-80ED-47E9-BDBE-24315FFBB908}"/>
   <bookViews>
-    <workbookView xWindow="-72" yWindow="2592" windowWidth="18216" windowHeight="12120" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-72" yWindow="2592" windowWidth="18216" windowHeight="12120" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -2049,7 +2049,7 @@
         <v>49</v>
       </c>
       <c r="F4" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>21</v>
